--- a/XBRL-template-MFRS/Group/08-SOCF-Direct.xlsx
+++ b/XBRL-template-MFRS/Group/08-SOCF-Direct.xlsx
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="B20" s="21">
-        <f>1*B8+1*B9+1*B10+1*B11+-1*B12+-1*B13+1*B14+-1*B15+1*B16+-1*B17+-1*B18+1*B19</f>
+        <f>1*B8+1*B9+1*B10+1*B11+1*B12+1*B13+1*B14+1*B15+1*B16+1*B17+1*B18+1*B19</f>
         <v/>
       </c>
       <c r="C20" s="21">
-        <f>1*C8+1*C9+1*C10+1*C11+-1*C12+-1*C13+1*C14+-1*C15+1*C16+-1*C17+-1*C18+1*C19</f>
+        <f>1*C8+1*C9+1*C10+1*C11+1*C12+1*C13+1*C14+1*C15+1*C16+1*C17+1*C18+1*C19</f>
         <v/>
       </c>
       <c r="D20" s="21">
-        <f>1*D8+1*D9+1*D10+1*D11+-1*D12+-1*D13+1*D14+-1*D15+1*D16+-1*D17+-1*D18+1*D19</f>
+        <f>1*D8+1*D9+1*D10+1*D11+1*D12+1*D13+1*D14+1*D15+1*D16+1*D17+1*D18+1*D19</f>
         <v/>
       </c>
       <c r="E20" s="21">
-        <f>1*E8+1*E9+1*E10+1*E11+-1*E12+-1*E13+1*E14+-1*E15+1*E16+-1*E17+-1*E18+1*E19</f>
+        <f>1*E8+1*E9+1*E10+1*E11+1*E12+1*E13+1*E14+1*E15+1*E16+1*E17+1*E18+1*E19</f>
         <v/>
       </c>
     </row>
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B52" s="21">
-        <f>1*B22+-1*B23+1*B24+-1*B25+1*B26+-1*B27+1*B28+-1*B29+-1*B30+-1*B31+1*B32+1*B33+-1*B34+1*B35+1*B36+1*B37+1*B38+1*B39+-1*B40+-1*B41+-1*B42+1*B43+1*B44+1*B45+-1*B46+-1*B47+1*B48+1*B49+1*B50+1*B51</f>
+        <f>1*B22+-1*B23+1*B24+-1*B25+1*B26+-1*B27+1*B28+-1*B29+1*B30+-1*B31+1*B32+-1*B33+1*B34+1*B35+1*B36+1*B37+1*B38+1*B39+-1*B40+-1*B41+-1*B42+1*B43+1*B44+1*B45+-1*B46+-1*B47+-1*B48+-1*B49+1*B50+1*B51</f>
         <v/>
       </c>
       <c r="C52" s="21">
-        <f>1*C22+-1*C23+1*C24+-1*C25+1*C26+-1*C27+1*C28+-1*C29+-1*C30+-1*C31+1*C32+1*C33+-1*C34+1*C35+1*C36+1*C37+1*C38+1*C39+-1*C40+-1*C41+-1*C42+1*C43+1*C44+1*C45+-1*C46+-1*C47+1*C48+1*C49+1*C50+1*C51</f>
+        <f>1*C22+-1*C23+1*C24+-1*C25+1*C26+-1*C27+1*C28+-1*C29+1*C30+-1*C31+1*C32+-1*C33+1*C34+1*C35+1*C36+1*C37+1*C38+1*C39+-1*C40+-1*C41+-1*C42+1*C43+1*C44+1*C45+-1*C46+-1*C47+-1*C48+-1*C49+1*C50+1*C51</f>
         <v/>
       </c>
       <c r="D52" s="21">
-        <f>1*D22+-1*D23+1*D24+-1*D25+1*D26+-1*D27+1*D28+-1*D29+-1*D30+-1*D31+1*D32+1*D33+-1*D34+1*D35+1*D36+1*D37+1*D38+1*D39+-1*D40+-1*D41+-1*D42+1*D43+1*D44+1*D45+-1*D46+-1*D47+1*D48+1*D49+1*D50+1*D51</f>
+        <f>1*D22+-1*D23+1*D24+-1*D25+1*D26+-1*D27+1*D28+-1*D29+1*D30+-1*D31+1*D32+-1*D33+1*D34+1*D35+1*D36+1*D37+1*D38+1*D39+-1*D40+-1*D41+-1*D42+1*D43+1*D44+1*D45+-1*D46+-1*D47+-1*D48+-1*D49+1*D50+1*D51</f>
         <v/>
       </c>
       <c r="E52" s="21">
-        <f>1*E22+-1*E23+1*E24+-1*E25+1*E26+-1*E27+1*E28+-1*E29+-1*E30+-1*E31+1*E32+1*E33+-1*E34+1*E35+1*E36+1*E37+1*E38+1*E39+-1*E40+-1*E41+-1*E42+1*E43+1*E44+1*E45+-1*E46+-1*E47+1*E48+1*E49+1*E50+1*E51</f>
+        <f>1*E22+-1*E23+1*E24+-1*E25+1*E26+-1*E27+1*E28+-1*E29+1*E30+-1*E31+1*E32+-1*E33+1*E34+1*E35+1*E36+1*E37+1*E38+1*E39+-1*E40+-1*E41+-1*E42+1*E43+1*E44+1*E45+-1*E46+-1*E47+-1*E48+-1*E49+1*E50+1*E51</f>
         <v/>
       </c>
     </row>
@@ -1334,19 +1334,19 @@
         </is>
       </c>
       <c r="B72" s="20">
-        <f>-1*B54+-1*B55+1*B56+1*B57+1*B58+1*B59+-1*B60+-1*B61+-1*B62+-1*B63+1*B64+-1*B65+-1*B66+1*B67+1*B68+-1*B69+-1*B70+1*B71</f>
+        <f>1*B54+1*B55+1*B56+1*B57+1*B58+1*B59+-1*B60+-1*B61+-1*B62+1*B63+1*B64+-1*B65+1*B66+1*B67+1*B68+-1*B69+-1*B70+1*B71</f>
         <v/>
       </c>
       <c r="C72" s="20">
-        <f>-1*C54+-1*C55+1*C56+1*C57+1*C58+1*C59+-1*C60+-1*C61+-1*C62+-1*C63+1*C64+-1*C65+-1*C66+1*C67+1*C68+-1*C69+-1*C70+1*C71</f>
+        <f>1*C54+1*C55+1*C56+1*C57+1*C58+1*C59+-1*C60+-1*C61+-1*C62+1*C63+1*C64+-1*C65+1*C66+1*C67+1*C68+-1*C69+-1*C70+1*C71</f>
         <v/>
       </c>
       <c r="D72" s="20">
-        <f>-1*D54+-1*D55+1*D56+1*D57+1*D58+1*D59+-1*D60+-1*D61+-1*D62+-1*D63+1*D64+-1*D65+-1*D66+1*D67+1*D68+-1*D69+-1*D70+1*D71</f>
+        <f>1*D54+1*D55+1*D56+1*D57+1*D58+1*D59+-1*D60+-1*D61+-1*D62+1*D63+1*D64+-1*D65+1*D66+1*D67+1*D68+-1*D69+-1*D70+1*D71</f>
         <v/>
       </c>
       <c r="E72" s="20">
-        <f>-1*E54+-1*E55+1*E56+1*E57+1*E58+1*E59+-1*E60+-1*E61+-1*E62+-1*E63+1*E64+-1*E65+-1*E66+1*E67+1*E68+-1*E69+-1*E70+1*E71</f>
+        <f>1*E54+1*E55+1*E56+1*E57+1*E58+1*E59+-1*E60+-1*E61+-1*E62+1*E63+1*E64+-1*E65+1*E66+1*E67+1*E68+-1*E69+-1*E70+1*E71</f>
         <v/>
       </c>
     </row>
